--- a/toy_models/farm_toy_v6_cash.xlsx
+++ b/toy_models/farm_toy_v6_cash.xlsx
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-08-30 14:05   (from source at commit 38a258a)</t>
+          <t>BUILT 2026-08-30 19:28   (from source at commit 28f7835)</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">           the PROFIT cell (B231).</t>
+          <t xml:space="preserve">           the PROFIT cell (B233).</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG260"/>
+  <dimension ref="A1:BG262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-08-30 14:05   (from source at 38a258a)</t>
+          <t>BUILT 2026-08-30 19:28   (from source at 28f7835)</t>
         </is>
       </c>
     </row>
@@ -28134,211 +28134,211 @@
         </is>
       </c>
       <c r="E220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="F220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="G220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="H220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="I220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="J220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="K220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="L220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="M220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="N220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="O220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="P220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="Q220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="R220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="S220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="T220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="U220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="V220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="W220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="X220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="Y220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="Z220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AA220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AB220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AC220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AD220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AE220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AF220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AG220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AH220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AI220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AJ220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AK220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AL220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AM220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AN220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AO220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AP220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AQ220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AR220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AS220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AT220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AU220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AV220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AW220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AX220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AY220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="AZ220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="BA220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="BB220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="BC220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
       <c r="BD220" s="35">
-        <f>-($B$204+$B$205)</f>
+        <f>-$B$205</f>
         <v/>
       </c>
     </row>
@@ -28560,403 +28560,383 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   This is the app's C13. Cash may go NEGATIVE — that is the credit line being drawn — but never below the floor.</t>
+          <t xml:space="preserve">   This is the app's C13. Cash may go NEGATIVE — that is the credit line being drawn — but never below the floor, which is the line fully drawn.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">   The app states the same rule the other way round: it constrains cumulative NET FLOW (which excludes</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   opening cash) against -(opening + credit). Both are the same constraint; mixing them double-counts the opening balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">   ⚠️ It barely binds here, because the biggest weekly outgoing a real farm has is PAYROLL, and labour is v7. Do not read this curve as realistic yet.</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="3" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
         <is>
           <t>8 — THE OPTIMIZER</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B226" s="50">
-        <f>SUM(E113:BD113)*$I$18+SUM(E119:BD119)*$I$19+SUM(E140:BD140)*$I$20+SUM(E148:BD148)*$I$21+SUM(E169:BD169)*$I$22+SUM(E175:BD175)*$I$23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>Growing cost</t>
-        </is>
-      </c>
-      <c r="B227" s="50">
-        <f>SUM(E212:BD212)</f>
-        <v/>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>seed at planting + fertiliser and fuel every week in the ground</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B228" s="50">
-        <f>SUM(E211:BD211)</f>
+        <f>SUM(E113:BD113)*$I$18+SUM(E119:BD119)*$I$19+SUM(E140:BD140)*$I$20+SUM(E148:BD148)*$I$21+SUM(E169:BD169)*$I$22+SUM(E175:BD175)*$I$23</f>
         <v/>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>Fixed cost</t>
+          <t>Growing cost</t>
         </is>
       </c>
       <c r="B229" s="50">
-        <f>SUM(E213:BD213)</f>
+        <f>SUM(E212:BD212)</f>
         <v/>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>owed all 52 weeks whatever you plant</t>
+          <t>seed at planting + fertiliser and fuel every week in the ground</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>Overhead</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="B230" s="50">
-        <f>SUM(E214:BD214)</f>
+        <f>SUM(E211:BD211)</f>
         <v/>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="21" t="inlineStr">
-        <is>
-          <t>PROFIT  (the objective)</t>
-        </is>
-      </c>
-      <c r="B231" s="52">
-        <f>B226-SUM(B227:B230)</f>
-        <v/>
-      </c>
-      <c r="C231" s="4" t="inlineStr">
-        <is>
-          <t>&lt;-- MAXIMISE THIS CELL</t>
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>Fixed cost</t>
+        </is>
+      </c>
+      <c r="B231" s="50">
+        <f>SUM(E213:BD213)</f>
+        <v/>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>owed all 52 weeks whatever you plant</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>Plantings chosen</t>
-        </is>
-      </c>
-      <c r="B232" s="53">
-        <f>SUM($D$28:$D$95)</f>
-        <v/>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>of 68 offered</t>
+          <t>Overhead</t>
+        </is>
+      </c>
+      <c r="B232" s="50">
+        <f>SUM(E214:BD214)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="21" t="inlineStr">
+        <is>
+          <t>PROFIT  (the objective)</t>
+        </is>
+      </c>
+      <c r="B233" s="52">
+        <f>B228-SUM(B229:B232)</f>
+        <v/>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>&lt;-- MAXIMISE THIS CELL</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
+          <t>Plantings chosen</t>
+        </is>
+      </c>
+      <c r="B234" s="53">
+        <f>SUM($D$28:$D$95)</f>
+        <v/>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>of 68 offered</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
           <t>Annual caps</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="25" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">   Kale / Wholesale — sold all year</t>
         </is>
       </c>
-      <c r="B235" s="35">
+      <c r="B237" s="35">
         <f>SUM(E148:BD148)</f>
         <v/>
       </c>
-      <c r="C235" s="33" t="inlineStr">
+      <c r="C237" s="33" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="D235" s="35">
+      <c r="D237" s="35">
         <f>$D$21</f>
         <v/>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="3" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
         <is>
           <t>SOLVER SETUP — Tools &gt; Solver</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="4" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
         <is>
           <t>Target cell</t>
         </is>
       </c>
-      <c r="B238" s="25" t="inlineStr">
-        <is>
-          <t>$B$231</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="inlineStr">
+      <c r="B240" s="25" t="inlineStr">
+        <is>
+          <t>$B$233</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>set to MAXIMUM</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="4" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
         <is>
           <t>By changing cells</t>
         </is>
       </c>
-      <c r="B239" s="25" t="inlineStr">
+      <c r="B241" s="25" t="inlineStr">
         <is>
           <t>$C$28:$D$95</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr">
         <is>
           <t>acres AND plant? together</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ...and</t>
-        </is>
-      </c>
-      <c r="B240" s="25" t="inlineStr">
-        <is>
-          <t>$E$112:$BD$112;$E$118:$BD$118;$E$139:$BD$139;$E$147:$BD$147;$E$168:$BD$168;$E$174:$BD$174</t>
-        </is>
-      </c>
-      <c r="G240" s="2" t="inlineStr">
-        <is>
-          <t>the OFFERED rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="25" t="inlineStr">
-        <is>
-          <t>Constraint — PLANT? is binary</t>
-        </is>
-      </c>
-      <c r="B241" s="25" t="inlineStr">
-        <is>
-          <t>$D$28:$D$95  =  Binary</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="25" t="inlineStr">
         <is>
-          <t>Constraint — C9 acres &lt;= max</t>
+          <t xml:space="preserve">  ...and</t>
         </is>
       </c>
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>$C$28:$C$95  &lt;=  $BE$28:$BE$95</t>
+          <t>$E$112:$BD$112;$E$118:$BD$118;$E$139:$BD$139;$E$147:$BD$147;$E$168:$BD$168;$E$174:$BD$174</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>no acres without deciding to plant</t>
+          <t>the OFFERED rows</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="25" t="inlineStr">
         <is>
-          <t>Constraint — C10 acres &gt;= min</t>
+          <t>Constraint — PLANT? is binary</t>
         </is>
       </c>
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>$C$28:$C$95  &gt;=  $BF$28:$BF$95</t>
-        </is>
-      </c>
-      <c r="G243" s="2" t="inlineStr">
-        <is>
-          <t>planted means a real block</t>
+          <t>$D$28:$D$95  =  Binary</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Spinach/Farmers Market sold &lt;= ceiling</t>
+          <t>Constraint — C9 acres &lt;= max</t>
         </is>
       </c>
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>$E$113:$BD$113  &lt;=  $E$111:$BD$111</t>
+          <t>$C$28:$C$95  &lt;=  $BE$28:$BE$95</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>no acres without deciding to plant</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Spinach/Wholesale sold &lt;= ceiling</t>
+          <t>Constraint — C10 acres &gt;= min</t>
         </is>
       </c>
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>$E$119:$BD$119  &lt;=  $E$117:$BD$117</t>
+          <t>$C$28:$C$95  &gt;=  $BF$28:$BF$95</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>planted means a real block</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Kale/Farmers Market sold &lt;= ceiling</t>
+          <t>Constraint — Spinach/Farmers Market sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>$E$140:$BD$140  &lt;=  $E$138:$BD$138</t>
+          <t>$E$113:$BD$113  &lt;=  $E$111:$BD$111</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Kale/Wholesale sold &lt;= ceiling</t>
+          <t>Constraint — Spinach/Wholesale sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>$E$148:$BD$148  &lt;=  $E$144:$BD$144</t>
+          <t>$E$119:$BD$119  &lt;=  $E$117:$BD$117</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Garlic/Farmers Market sold &lt;= ceiling</t>
+          <t>Constraint — Kale/Farmers Market sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>$E$169:$BD$169  &lt;=  $E$167:$BD$167</t>
+          <t>$E$140:$BD$140  &lt;=  $E$138:$BD$138</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Garlic/Wholesale sold &lt;= ceiling</t>
+          <t>Constraint — Kale/Wholesale sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>$E$175:$BD$175  &lt;=  $E$173:$BD$173</t>
+          <t>$E$148:$BD$148  &lt;=  $E$144:$BD$144</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Spinach stock never negative</t>
+          <t>Constraint — Garlic/Farmers Market sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>$E$123:$BD$123  &gt;=  0</t>
+          <t>$E$169:$BD$169  &lt;=  $E$167:$BD$167</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Kale stock never negative</t>
+          <t>Constraint — Garlic/Wholesale sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>$E$152:$BD$152  &gt;=  0</t>
+          <t>$E$175:$BD$175  &lt;=  $E$173:$BD$173</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Garlic stock never negative</t>
+          <t>Constraint — Spinach stock never negative</t>
         </is>
       </c>
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>$E$179:$BD$179  &gt;=  0</t>
+          <t>$E$123:$BD$123  &gt;=  0</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Spinach shelf life</t>
+          <t>Constraint — Kale stock never negative</t>
         </is>
       </c>
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>$E$123:$BD$123  &lt;=  $E$126:$BD$126</t>
-        </is>
-      </c>
-      <c r="G253" s="2" t="inlineStr">
-        <is>
-          <t>nothing held longer than it keeps</t>
+          <t>$E$152:$BD$152  &gt;=  0</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Kale shelf life</t>
+          <t>Constraint — Garlic stock never negative</t>
         </is>
       </c>
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>$E$152:$BD$152  &lt;=  $E$155:$BD$155</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>nothing held longer than it keeps</t>
+          <t>$E$179:$BD$179  &gt;=  0</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="25" t="inlineStr">
         <is>
-          <t>Constraint — Garlic shelf life</t>
+          <t>Constraint — Spinach shelf life</t>
         </is>
       </c>
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>$E$179:$BD$179  &lt;=  $E$182:$BD$182</t>
+          <t>$E$123:$BD$123  &lt;=  $E$126:$BD$126</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -28968,68 +28948,102 @@
     <row r="256">
       <c r="A256" s="25" t="inlineStr">
         <is>
-          <t>Constraint — cold store</t>
+          <t>Constraint — Kale shelf life</t>
         </is>
       </c>
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>$E$190:$BD$190  &lt;=  $B$6</t>
+          <t>$E$152:$BD$152  &lt;=  $E$155:$BD$155</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>nothing held longer than it keeps</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="25" t="inlineStr">
         <is>
-          <t>Constraint — ambient store</t>
+          <t>Constraint — Garlic shelf life</t>
         </is>
       </c>
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>$E$197:$BD$197  &lt;=  $B$7</t>
+          <t>$E$179:$BD$179  &lt;=  $E$182:$BD$182</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>nothing held longer than it keeps</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="25" t="inlineStr">
         <is>
-          <t>Constraint — land</t>
+          <t>Constraint — cold store</t>
         </is>
       </c>
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>$E$99:$BD$99  &lt;=  $B$5</t>
+          <t>$E$190:$BD$190  &lt;=  $B$6</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="25" t="inlineStr">
         <is>
+          <t>Constraint — ambient store</t>
+        </is>
+      </c>
+      <c r="B259" s="25" t="inlineStr">
+        <is>
+          <t>$E$197:$BD$197  &lt;=  $B$7</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="25" t="inlineStr">
+        <is>
+          <t>Constraint — land</t>
+        </is>
+      </c>
+      <c r="B260" s="25" t="inlineStr">
+        <is>
+          <t>$E$99:$BD$99  &lt;=  $B$5</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="25" t="inlineStr">
+        <is>
           <t>Constraint — CASH FLOOR</t>
         </is>
       </c>
-      <c r="B259" s="25" t="inlineStr">
+      <c r="B261" s="25" t="inlineStr">
         <is>
           <t>$E$218:$BD$218  &gt;=  $E$220:$BD$220</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr">
         <is>
           <t>the app's C13</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="B260" s="25" t="inlineStr">
+      <c r="B262" s="25" t="inlineStr">
         <is>
           <t>engine = LibreOffice CoinMP Linear Solver</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr">
         <is>
           <t>tick 'Assume variables as non-negative'</t>
         </is>
